--- a/NBFC_CRM_Windows11_Chatbot.xlsx
+++ b/NBFC_CRM_Windows11_Chatbot.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Customer_Master" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="47">
   <si>
     <t>Customer_ID</t>
   </si>
@@ -122,9 +122,6 @@
     <t>Active</t>
   </si>
   <si>
-    <t>LAN10002</t>
-  </si>
-  <si>
     <t>Two Wheeler Loan</t>
   </si>
   <si>
@@ -153,6 +150,18 @@
   </si>
   <si>
     <t>2026-05-05</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>10001</t>
+  </si>
+  <si>
+    <t>10002</t>
   </si>
 </sst>
 </file>
@@ -188,8 +197,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -525,8 +535,8 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>8</v>
+      <c r="A2" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
@@ -551,8 +561,8 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>14</v>
+      <c r="A3" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
@@ -622,8 +632,8 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>30</v>
+      <c r="A2" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
@@ -657,14 +667,14 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>33</v>
+      <c r="A3" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3">
         <v>90000</v>
@@ -706,25 +716,25 @@
         <v>20</v>
       </c>
       <c r="B1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" t="s">
         <v>35</v>
-      </c>
-      <c r="C1" t="s">
-        <v>36</v>
       </c>
       <c r="D1" t="s">
         <v>27</v>
       </c>
       <c r="E1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" t="s">
         <v>37</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>38</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>39</v>
-      </c>
-      <c r="H1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -735,7 +745,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D2">
         <v>12000</v>
@@ -750,7 +760,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -761,7 +771,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D3">
         <v>12000</v>
@@ -776,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/NBFC_CRM_Windows11_Chatbot.xlsx
+++ b/NBFC_CRM_Windows11_Chatbot.xlsx
@@ -14,14 +14,13 @@
   <sheets>
     <sheet name="Customer_Master" sheetId="1" r:id="rId1"/>
     <sheet name="Loan_Details" sheetId="2" r:id="rId2"/>
-    <sheet name="EMI_Details" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="41">
   <si>
     <t>Customer_ID</t>
   </si>
@@ -32,7 +31,7 @@
     <t>Mobile_Number</t>
   </si>
   <si>
-    <t>Email</t>
+    <t>Address</t>
   </si>
   <si>
     <t>City</t>
@@ -41,112 +40,109 @@
     <t>State</t>
   </si>
   <si>
-    <t>Customer_Segment</t>
-  </si>
-  <si>
-    <t>KYC_Status</t>
+    <t>Pincode</t>
+  </si>
+  <si>
+    <t>Email_ID</t>
+  </si>
+  <si>
+    <t>GST_Number</t>
   </si>
   <si>
     <t>Rahul Sharma</t>
   </si>
   <si>
-    <t>rahul@email.com</t>
+    <t>9876543210</t>
+  </si>
+  <si>
+    <t>12 MG Road</t>
   </si>
   <si>
     <t>Delhi</t>
   </si>
   <si>
-    <t>Retail</t>
-  </si>
-  <si>
-    <t>Verified</t>
+    <t>110001</t>
+  </si>
+  <si>
+    <t>rahul@gmail.com</t>
+  </si>
+  <si>
+    <t>07ABCDE1234F1Z5</t>
   </si>
   <si>
     <t>Anita Verma</t>
   </si>
   <si>
-    <t>9812345678</t>
-  </si>
-  <si>
-    <t>anita@email.com</t>
-  </si>
-  <si>
-    <t>Noida</t>
-  </si>
-  <si>
-    <t>UP</t>
+    <t>9123456780</t>
+  </si>
+  <si>
+    <t>Park Street</t>
+  </si>
+  <si>
+    <t>Kolkata</t>
+  </si>
+  <si>
+    <t>West Bengal</t>
+  </si>
+  <si>
+    <t>700016</t>
+  </si>
+  <si>
+    <t>anita@gmail.com</t>
+  </si>
+  <si>
+    <t>19ABCDE4321F1Z3</t>
+  </si>
+  <si>
+    <t>Mohan Singh</t>
+  </si>
+  <si>
+    <t>9988776655</t>
+  </si>
+  <si>
+    <t>Sector 21</t>
+  </si>
+  <si>
+    <t>Chandigarh</t>
+  </si>
+  <si>
+    <t>160022</t>
+  </si>
+  <si>
+    <t>mohan@gmail.com</t>
+  </si>
+  <si>
+    <t>04ABCDE5678F1Z2</t>
   </si>
   <si>
     <t>Loan_Account_Number</t>
   </si>
   <si>
-    <t>Loan_Type</t>
-  </si>
-  <si>
     <t>Loan_Amount</t>
   </si>
   <si>
+    <t>EMI_Amount</t>
+  </si>
+  <si>
     <t>Principal_Outstanding</t>
   </si>
   <si>
     <t>Interest_Outstanding</t>
   </si>
   <si>
+    <t>Charges_Outstanding</t>
+  </si>
+  <si>
+    <t>Interest_Rate</t>
+  </si>
+  <si>
     <t>Balance_Principal</t>
   </si>
   <si>
-    <t>Charges_Outstanding</t>
-  </si>
-  <si>
-    <t>EMI_Amount</t>
-  </si>
-  <si>
-    <t>Interest_Rate</t>
-  </si>
-  <si>
     <t>Loan_Status</t>
   </si>
   <si>
-    <t>Personal Loan</t>
-  </si>
-  <si>
     <t>Active</t>
-  </si>
-  <si>
-    <t>Two Wheeler Loan</t>
-  </si>
-  <si>
-    <t>EMI_Number</t>
-  </si>
-  <si>
-    <t>Due_Date</t>
-  </si>
-  <si>
-    <t>Principal_Component</t>
-  </si>
-  <si>
-    <t>Interest_Component</t>
-  </si>
-  <si>
-    <t>Late_Fee</t>
-  </si>
-  <si>
-    <t>Payment_Status</t>
-  </si>
-  <si>
-    <t>2026-04-05</t>
-  </si>
-  <si>
-    <t>Pending</t>
-  </si>
-  <si>
-    <t>2026-05-05</t>
-  </si>
-  <si>
-    <t>10001</t>
-  </si>
-  <si>
-    <t>10002</t>
   </si>
 </sst>
 </file>
@@ -182,9 +178,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -487,13 +482,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="3" max="3" width="10.81640625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -518,57 +510,95 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2">
         <v>1011</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2">
-        <v>9560665511</v>
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3">
         <v>1012</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H3" t="s">
-        <v>12</v>
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1013</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -578,200 +608,135 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="E1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F1" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="G1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="H1" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="I1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="J1" t="s">
-        <v>26</v>
-      </c>
-      <c r="K1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>10001</v>
+      </c>
+      <c r="B2">
+        <v>1011</v>
+      </c>
+      <c r="C2">
+        <v>250000</v>
+      </c>
+      <c r="D2">
+        <v>5500</v>
+      </c>
+      <c r="E2">
+        <v>180000</v>
+      </c>
+      <c r="F2">
+        <v>12000</v>
+      </c>
+      <c r="G2">
+        <v>3000</v>
+      </c>
+      <c r="H2">
+        <v>11.5</v>
+      </c>
+      <c r="I2">
+        <v>170000</v>
+      </c>
+      <c r="J2" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="1">
-        <v>1011</v>
-      </c>
-      <c r="C2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2">
-        <v>500000</v>
-      </c>
-      <c r="E2">
-        <v>350000</v>
-      </c>
-      <c r="F2">
-        <v>25000</v>
-      </c>
-      <c r="G2">
-        <v>325000</v>
-      </c>
-      <c r="H2">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>10002</v>
+      </c>
+      <c r="B3">
+        <v>1012</v>
+      </c>
+      <c r="C3">
+        <v>180000</v>
+      </c>
+      <c r="D3">
+        <v>4200</v>
+      </c>
+      <c r="E3">
+        <v>140000</v>
+      </c>
+      <c r="F3">
+        <v>9000</v>
+      </c>
+      <c r="G3">
         <v>1500</v>
       </c>
-      <c r="I2">
-        <v>12000</v>
-      </c>
-      <c r="J2">
-        <v>12.5</v>
-      </c>
-      <c r="K2" t="s">
-        <v>29</v>
+      <c r="H3">
+        <v>12</v>
+      </c>
+      <c r="I3">
+        <v>132000</v>
+      </c>
+      <c r="J3" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="1">
-        <v>1012</v>
-      </c>
-      <c r="C3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3">
-        <v>90000</v>
-      </c>
-      <c r="E3">
-        <v>40000</v>
-      </c>
-      <c r="F3">
-        <v>3000</v>
-      </c>
-      <c r="G3">
-        <v>37000</v>
-      </c>
-      <c r="H3">
-        <v>500</v>
-      </c>
-      <c r="I3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>10003</v>
+      </c>
+      <c r="B4">
+        <v>1013</v>
+      </c>
+      <c r="C4">
+        <v>320000</v>
+      </c>
+      <c r="D4">
+        <v>7200</v>
+      </c>
+      <c r="E4">
+        <v>260000</v>
+      </c>
+      <c r="F4">
+        <v>15000</v>
+      </c>
+      <c r="G4">
         <v>3500</v>
       </c>
-      <c r="J3">
-        <v>10.5</v>
-      </c>
-      <c r="K3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="H4">
+        <v>10.75</v>
+      </c>
+      <c r="I4">
+        <v>250000</v>
+      </c>
+      <c r="J4" t="s">
         <v>40</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2">
-        <v>12000</v>
-      </c>
-      <c r="E2">
-        <v>9000</v>
-      </c>
-      <c r="F2">
-        <v>3000</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3">
-        <v>12000</v>
-      </c>
-      <c r="E3">
-        <v>9100</v>
-      </c>
-      <c r="F3">
-        <v>2900</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/NBFC_CRM_Windows11_Chatbot.xlsx
+++ b/NBFC_CRM_Windows11_Chatbot.xlsx
@@ -52,9 +52,6 @@
     <t>Rahul Sharma</t>
   </si>
   <si>
-    <t>9876543210</t>
-  </si>
-  <si>
     <t>12 MG Road</t>
   </si>
   <si>
@@ -143,6 +140,9 @@
   </si>
   <si>
     <t>Active</t>
+  </si>
+  <si>
+    <t>9560665511</t>
   </si>
 </sst>
 </file>
@@ -178,8 +178,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -484,6 +485,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.36328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -521,26 +533,26 @@
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>13</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>14</v>
-      </c>
-      <c r="I2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -548,28 +560,28 @@
         <v>1012</v>
       </c>
       <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>20</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>21</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>22</v>
-      </c>
-      <c r="I3" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -577,28 +589,28 @@
         <v>1013</v>
       </c>
       <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>25</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>26</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
         <v>27</v>
       </c>
-      <c r="F4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>28</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>29</v>
-      </c>
-      <c r="I4" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -613,34 +625,34 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" t="s">
         <v>32</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>33</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>34</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>35</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>36</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>37</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>38</v>
-      </c>
-      <c r="J1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -672,7 +684,7 @@
         <v>170000</v>
       </c>
       <c r="J2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -704,7 +716,7 @@
         <v>132000</v>
       </c>
       <c r="J3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -736,7 +748,7 @@
         <v>250000</v>
       </c>
       <c r="J4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
